--- a/astro-site/public/dl/coffee-shop-checklist-templates/04-barista-checklist-duties-by-role.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/04-barista-checklist-duties-by-role.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>7:00 AM</t>
+          <t>6:30 AM</t>
         </is>
       </c>
       <c r="F6" s="30" t="n"/>
@@ -1641,9 +1641,9 @@
       <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Brew the drip / batch brew</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Brew the drip / batch brew (and filter the cold brew, if you serve it)</t>
         </is>
       </c>
       <c r="C11" s="29" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>Pull product from the case and store in the walk-in</t>
+          <t>Pull product from the case: TCS items to the cooler, dry baked goods covered and dated</t>
         </is>
       </c>
       <c r="C17" s="29" t="inlineStr">
@@ -3740,9 +3740,9 @@
       <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>Final dish area: wash all remaining dishes</t>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>Final dish area: wash all remaining dishes and check the dish machine's sanitizer with a test strip (or the final-rinse temperature on its data plate)</t>
         </is>
       </c>
       <c r="C17" s="29" t="inlineStr">
